--- a/food_beverage_order_forms/004_easter_brunch_order_form--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/004_easter_brunch_order_form--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'guest_count_one',_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'guest_count_one', 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'guest_count_two',_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'guest_count_two', 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'guest_count_three',_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'guest_count_three', 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'guest_count_four',_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'guest_count_four', 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'easter_brunch_egg_hunter',_'label':_'easter_brunch_egg_hunt_game'}</t>
+          <t>easter_brunch_egg_hunt_game</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'easter_brunch_egg_hunter', 'label': 'Easter Brunch Egg Hunt Game'}</t>
+          <t>Easter Brunch Egg Hunt Game</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'easter_brunch_food',_'label':_'easter_brunch_food'}</t>
+          <t>easter_brunch_food</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'easter_brunch_food', 'label': 'Easter Brunch Food'}</t>
+          <t>Easter Brunch Food</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'easter_brunch_drinks',_'label':_'easter_brunch_drinks'}</t>
+          <t>easter_brunch_drinks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'easter_brunch_drinks', 'label': 'Easter Brunch Drinks'}</t>
+          <t>Easter Brunch Drinks</t>
         </is>
       </c>
     </row>
